--- a/artfynd/A 44319-2024 artfynd.xlsx
+++ b/artfynd/A 44319-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796579</v>
+        <v>119796570</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768359</v>
+        <v>768327</v>
       </c>
       <c r="R2" t="n">
-        <v>7461670</v>
+        <v>7461630</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>119796571</v>
       </c>
       <c r="B3" t="n">
-        <v>89252</v>
+        <v>89269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796574</v>
+        <v>119796577</v>
       </c>
       <c r="B4" t="n">
-        <v>91856</v>
+        <v>89650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768420</v>
+        <v>768336</v>
       </c>
       <c r="R4" t="n">
-        <v>7461700</v>
+        <v>7461710</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796576</v>
+        <v>119796572</v>
       </c>
       <c r="B5" t="n">
-        <v>89252</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768422</v>
+        <v>768492</v>
       </c>
       <c r="R5" t="n">
-        <v>7461690</v>
+        <v>7461610</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796572</v>
+        <v>119796573</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768492</v>
+        <v>768503</v>
       </c>
       <c r="R6" t="n">
-        <v>7461610</v>
+        <v>7461690</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796570</v>
+        <v>119796578</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>89269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768327</v>
+        <v>768340</v>
       </c>
       <c r="R7" t="n">
-        <v>7461630</v>
+        <v>7461700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796577</v>
+        <v>119796579</v>
       </c>
       <c r="B8" t="n">
-        <v>89633</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768336</v>
+        <v>768359</v>
       </c>
       <c r="R8" t="n">
-        <v>7461710</v>
+        <v>7461670</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796573</v>
+        <v>119796574</v>
       </c>
       <c r="B9" t="n">
-        <v>91826</v>
+        <v>91874</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768503</v>
+        <v>768420</v>
       </c>
       <c r="R9" t="n">
-        <v>7461690</v>
+        <v>7461700</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796578</v>
+        <v>119796576</v>
       </c>
       <c r="B10" t="n">
-        <v>89252</v>
+        <v>89269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768340</v>
+        <v>768422</v>
       </c>
       <c r="R10" t="n">
-        <v>7461700</v>
+        <v>7461690</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 44319-2024 artfynd.xlsx
+++ b/artfynd/A 44319-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796570</v>
+        <v>119796578</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>89269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768327</v>
+        <v>768340</v>
       </c>
       <c r="R2" t="n">
-        <v>7461630</v>
+        <v>7461700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796571</v>
+        <v>119796579</v>
       </c>
       <c r="B3" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768456</v>
+        <v>768359</v>
       </c>
       <c r="R3" t="n">
-        <v>7461620</v>
+        <v>7461670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796577</v>
+        <v>119796573</v>
       </c>
       <c r="B4" t="n">
-        <v>89650</v>
+        <v>91844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1962</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768336</v>
+        <v>768503</v>
       </c>
       <c r="R4" t="n">
-        <v>7461710</v>
+        <v>7461690</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796572</v>
+        <v>119796577</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>89650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768492</v>
+        <v>768336</v>
       </c>
       <c r="R5" t="n">
-        <v>7461610</v>
+        <v>7461710</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796573</v>
+        <v>119796572</v>
       </c>
       <c r="B6" t="n">
-        <v>91844</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>768503</v>
+        <v>768492</v>
       </c>
       <c r="R6" t="n">
-        <v>7461690</v>
+        <v>7461610</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796578</v>
+        <v>119796570</v>
       </c>
       <c r="B7" t="n">
-        <v>89269</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>768340</v>
+        <v>768327</v>
       </c>
       <c r="R7" t="n">
-        <v>7461700</v>
+        <v>7461630</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796579</v>
+        <v>119796574</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>768359</v>
+        <v>768420</v>
       </c>
       <c r="R8" t="n">
-        <v>7461670</v>
+        <v>7461700</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796574</v>
+        <v>119796576</v>
       </c>
       <c r="B9" t="n">
-        <v>91874</v>
+        <v>89269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>768420</v>
+        <v>768422</v>
       </c>
       <c r="R9" t="n">
-        <v>7461700</v>
+        <v>7461690</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796576</v>
+        <v>119796571</v>
       </c>
       <c r="B10" t="n">
         <v>89269</v>
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>768422</v>
+        <v>768456</v>
       </c>
       <c r="R10" t="n">
-        <v>7461690</v>
+        <v>7461620</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
